--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:26:54+00:00</t>
+    <t>2025-01-23T13:26:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T13:26:37+00:00</t>
+    <t>2025-01-24T17:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T17:22:23+00:00</t>
+    <t>2025-01-29T14:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T14:25:50+00:00</t>
+    <t>2025-01-29T15:50:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T15:50:40+00:00</t>
+    <t>2025-01-30T15:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T15:03:39+00:00</t>
+    <t>2025-01-31T08:45:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T08:45:39+00:00</t>
+    <t>2025-02-18T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="157">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>assignedAuthor contient les éléments permettant de décrire l’auteur.</t>
+    <t>L'élément de l'en-tête du CDA assignedAuthor contient les éléments permettant de décrire l’auteur.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -404,6 +404,14 @@
     <t>AssignedAuthor.id</t>
   </si>
   <si>
+    <t>Identifiant de l’auteur : 
+- Obligatoire pour un professionnel 
+- Obligatoire pour le patient/usager 
+- Obligatoire pour un système de structure 
+- Obligatoire pour un SNR 
+- Obligatoire pour le DP</t>
+  </si>
+  <si>
     <t>AssignedAuthor.id.nullFlavor</t>
   </si>
   <si>
@@ -416,10 +424,20 @@
     <t>AssignedAuthor.id.root</t>
   </si>
   <si>
+    <t>- Pour un professionnel : '1.2.250.1.71.4.2.1'
+- Pour le patient/usager : OID de l'autorité d'affectation de l'INS
+- Pour un système de structure : '1.2.250.1.71.4.2.1' 
+- Pour un SNR : OID de l'éditeur 
+- Pour le DP : '1.2.250.1.71.4.2.1'</t>
+  </si>
+  <si>
     <t>A unique identifier that guarantees the global uniqueness of the instance identifier. The root alone may be the entire instance identifier.</t>
   </si>
   <si>
     <t>AssignedAuthor.id.extension</t>
+  </si>
+  <si>
+    <t>Valeur de l’identifiant</t>
   </si>
   <si>
     <t>AssignedAuthor.sdtcIdentifiedBy</t>
@@ -436,6 +454,14 @@
 </t>
   </si>
   <si>
+    <t>Profession / savoir-faire ou rôle : 
+- Obligatoire pour un professionnel 
+- Ne pas utiliser pour le patient/usager 
+- Obligatoire pour un système de structure 
+- Obligatoire pour un SNR 
+- Obligatoire pour le DP</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS</t>
   </si>
   <si>
@@ -446,6 +472,9 @@
 </t>
   </si>
   <si>
+    <t>Adresse géopostale de l’auteur</t>
+  </si>
+  <si>
     <t>AssignedAuthor.telecom</t>
   </si>
   <si>
@@ -453,6 +482,9 @@
 </t>
   </si>
   <si>
+    <t>Coordonnées télécom de l’auteur</t>
+  </si>
+  <si>
     <t>AssignedAuthor.assignedPerson</t>
   </si>
   <si>
@@ -460,6 +492,14 @@
 </t>
   </si>
   <si>
+    <t>Identité de l’auteur :  
+- Obligatoire pour un professionnel 
+- Obligatoire pour le patient/usager 
+- Ne pas utiliser pour un système de structure 
+- Ne pas utiliser pour un SNR 
+- Ne pas utiliser pour le DP</t>
+  </si>
+  <si>
     <t>AssignedAuthor.assignedAuthoringDevice</t>
   </si>
   <si>
@@ -467,11 +507,27 @@
 </t>
   </si>
   <si>
+    <t>Informations complémentaires si l’auteur est un système :
+- Ne pas utiliser pour un professionnel 
+- Ne pas utiliser pour le patient/usager 
+- Obligatoire pour un système de structure 
+- Obligatoire pour un SNR 
+- Obligatoire pour le DP</t>
+  </si>
+  <si>
     <t>AssignedAuthor.representedOrganization</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organization {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-represented-organization}
 </t>
+  </si>
+  <si>
+    <t>Structure correspondante : 
+- Obligatoire pour un professionnel 
+- Ne pas utiliser pour le patient/usager 
+- Obligatoire pour un système de structure 
+- Obligatoire pour un SNR 
+- Obligatoire pour le DP</t>
   </si>
 </sst>
 </file>
@@ -2074,7 +2130,9 @@
       <c r="K13" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="L13" s="2"/>
+      <c r="L13" t="s" s="2">
+        <v>127</v>
+      </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2145,10 +2203,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2246,10 +2304,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2262,7 +2320,7 @@
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>74</v>
@@ -2349,10 +2407,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2365,7 +2423,7 @@
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>74</v>
@@ -2452,10 +2510,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2465,7 +2523,7 @@
         <v>111</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>75</v>
@@ -2482,9 +2540,11 @@
       <c r="K17" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L17" s="2"/>
+      <c r="L17" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="M17" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2555,10 +2615,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2568,7 +2628,7 @@
         <v>117</v>
       </c>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>75</v>
@@ -2585,7 +2645,9 @@
       <c r="K18" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L18" s="2"/>
+      <c r="L18" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="M18" t="s" s="2">
         <v>118</v>
       </c>
@@ -2658,10 +2720,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2684,7 +2746,7 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -2737,7 +2799,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2757,10 +2819,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2783,9 +2845,11 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L20" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2816,7 +2880,7 @@
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>74</v>
@@ -2834,7 +2898,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -2854,10 +2918,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2880,9 +2944,11 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L21" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2933,7 +2999,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -2953,10 +3019,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2979,9 +3045,11 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="L22" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3032,7 +3100,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3052,10 +3120,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3078,9 +3146,11 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="L23" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3131,7 +3201,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3151,10 +3221,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3177,9 +3247,11 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="L24" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3230,7 +3302,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3250,10 +3322,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3276,9 +3348,11 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="L25" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3329,7 +3403,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T15:18:09+00:00</t>
+    <t>2025-02-23T14:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-23T14:02:58+00:00</t>
+    <t>2025-02-24T10:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:33:29+00:00</t>
+    <t>2025-02-24T11:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:08:59+00:00</t>
+    <t>2025-02-24T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T14:08:41+00:00</t>
+    <t>2025-02-25T09:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
